--- a/invoice-generator/templates/modern.xlsx
+++ b/invoice-generator/templates/modern.xlsx
@@ -1040,6 +1040,9 @@
     <mergeCell ref="A40:F41"/>
     <mergeCell ref="A45:F45"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="A45" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
   <pageSetup paperSize="1" orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
 </worksheet>
